--- a/data/department_tracking.xlsx
+++ b/data/department_tracking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ADriscoll/Documents/GitHub/implied_data/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3362D45C-077C-B04A-9F80-EC19AB090086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{933A2134-A5C9-C34B-A445-64CC60079C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17060" xr2:uid="{484B642E-F565-954E-B324-BC6070DF60AE}"/>
+    <workbookView xWindow="8220" yWindow="760" windowWidth="21900" windowHeight="17060" xr2:uid="{484B642E-F565-954E-B324-BC6070DF60AE}"/>
   </bookViews>
   <sheets>
     <sheet name="letters" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="258">
   <si>
     <t>name</t>
   </si>
@@ -802,6 +802,18 @@
   </si>
   <si>
     <t>date</t>
+  </si>
+  <si>
+    <t>Independent Budget</t>
+  </si>
+  <si>
+    <t>only charter exists</t>
+  </si>
+  <si>
+    <t>complex</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -876,67 +888,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -988,10 +940,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1311,18 +1259,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E8848C-B962-5745-8655-3C2761762076}">
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="4" width="14.5" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="11" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1342,25 +1290,31 @@
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -1380,13 +1334,13 @@
         <v>45</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46170</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46170</v>
+        <v>257</v>
+      </c>
+      <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
       </c>
       <c r="J2" s="3">
         <v>46170</v>
@@ -1394,11 +1348,17 @@
       <c r="K2" s="3">
         <v>46170</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M2" s="3">
+        <v>46170</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>74</v>
       </c>
@@ -1417,14 +1377,8 @@
       <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>252</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46171</v>
-      </c>
-      <c r="I3" s="3">
-        <v>46171</v>
       </c>
       <c r="J3" s="3">
         <v>46171</v>
@@ -1432,11 +1386,17 @@
       <c r="K3" s="3">
         <v>46171</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="3">
+        <v>46171</v>
+      </c>
+      <c r="M3" s="3">
+        <v>46171</v>
+      </c>
+      <c r="N3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>79</v>
       </c>
@@ -1452,14 +1412,8 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>252</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46156</v>
-      </c>
-      <c r="I4" s="3">
-        <v>46156</v>
       </c>
       <c r="J4" s="3">
         <v>46156</v>
@@ -1467,17 +1421,23 @@
       <c r="K4" s="3">
         <v>46156</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="3">
+        <v>46156</v>
+      </c>
+      <c r="M4" s="3">
+        <v>46156</v>
+      </c>
+      <c r="N4" t="s">
         <v>81</v>
       </c>
-      <c r="M4" t="s">
+      <c r="O4" t="s">
         <v>82</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -1493,14 +1453,8 @@
       <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>252</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46161</v>
-      </c>
-      <c r="I5" s="3">
-        <v>46161</v>
       </c>
       <c r="J5" s="3">
         <v>46161</v>
@@ -1508,8 +1462,14 @@
       <c r="K5" s="3">
         <v>46161</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L5" s="3">
+        <v>46161</v>
+      </c>
+      <c r="M5" s="3">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>97</v>
       </c>
@@ -1525,14 +1485,8 @@
       <c r="F6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>252</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46164</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46164</v>
       </c>
       <c r="J6" s="3">
         <v>46164</v>
@@ -1540,8 +1494,14 @@
       <c r="K6" s="3">
         <v>46164</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L6" s="3">
+        <v>46164</v>
+      </c>
+      <c r="M6" s="3">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>102</v>
       </c>
@@ -1557,14 +1517,8 @@
       <c r="F7" t="s">
         <v>17</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>252</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46170</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46170</v>
       </c>
       <c r="J7" s="3">
         <v>46170</v>
@@ -1572,14 +1526,20 @@
       <c r="K7" s="3">
         <v>46170</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M7" s="3">
+        <v>46170</v>
+      </c>
+      <c r="N7" t="s">
         <v>71</v>
       </c>
-      <c r="M7" t="s">
+      <c r="O7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -1595,14 +1555,8 @@
       <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>252</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46170</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46170</v>
       </c>
       <c r="J8" s="3">
         <v>46170</v>
@@ -1610,8 +1564,14 @@
       <c r="K8" s="3">
         <v>46170</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L8" s="3">
+        <v>46170</v>
+      </c>
+      <c r="M8" s="3">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1627,11 +1587,11 @@
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1647,11 +1607,11 @@
       <c r="F10" t="s">
         <v>17</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1667,11 +1627,11 @@
       <c r="F11" t="s">
         <v>13</v>
       </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1687,11 +1647,11 @@
       <c r="F12" t="s">
         <v>17</v>
       </c>
-      <c r="G12" t="s">
+      <c r="I12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -1707,11 +1667,11 @@
       <c r="F13" t="s">
         <v>17</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1727,14 +1687,14 @@
       <c r="F14" t="s">
         <v>31</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>0</v>
       </c>
-      <c r="L14" t="s">
+      <c r="N14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1750,14 +1710,14 @@
       <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>0</v>
       </c>
-      <c r="L15" s="5" t="s">
+      <c r="N15" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -1773,11 +1733,11 @@
       <c r="F16" t="s">
         <v>17</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -1793,11 +1753,11 @@
       <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1810,11 +1770,11 @@
       <c r="E18">
         <v>4</v>
       </c>
-      <c r="G18">
+      <c r="I18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1830,11 +1790,11 @@
       <c r="F19" t="s">
         <v>45</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -1850,11 +1810,11 @@
       <c r="F20" t="s">
         <v>45</v>
       </c>
-      <c r="G20">
+      <c r="I20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1870,11 +1830,13 @@
       <c r="F21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1890,14 +1852,14 @@
       <c r="F22" t="s">
         <v>56</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>0</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="N22" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1913,11 +1875,11 @@
       <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1933,11 +1895,13 @@
       <c r="F24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>61</v>
       </c>
@@ -1954,11 +1918,11 @@
       <c r="F25" t="s">
         <v>13</v>
       </c>
-      <c r="G25">
+      <c r="I25">
         <v>0.33</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
@@ -1975,11 +1939,11 @@
       <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>0.33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1995,17 +1959,17 @@
       <c r="F27" t="s">
         <v>17</v>
       </c>
-      <c r="G27">
+      <c r="I27">
         <v>0.66</v>
       </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>68</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="O27" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -2021,14 +1985,14 @@
       <c r="F28" t="s">
         <v>17</v>
       </c>
-      <c r="G28">
+      <c r="I28">
         <v>0.66</v>
       </c>
-      <c r="L28" t="s">
+      <c r="N28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -2044,14 +2008,14 @@
       <c r="F29" t="s">
         <v>17</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>0.66</v>
       </c>
-      <c r="L29" t="s">
+      <c r="N29" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -2067,11 +2031,11 @@
       <c r="F30" t="s">
         <v>17</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>0.66</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -2087,18 +2051,18 @@
       <c r="F31" t="s">
         <v>17</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
         <v>252</v>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
-      <c r="L31" t="s">
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -2114,17 +2078,17 @@
       <c r="F32" t="s">
         <v>17</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>252</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>46161</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>46161</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>89</v>
       </c>
@@ -2140,17 +2104,17 @@
       <c r="F33" t="s">
         <v>17</v>
       </c>
-      <c r="G33" t="s">
+      <c r="I33" t="s">
         <v>252</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>46162</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>46162</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>91</v>
       </c>
@@ -2166,17 +2130,17 @@
       <c r="F34" t="s">
         <v>17</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
         <v>252</v>
       </c>
-      <c r="H34" s="3">
+      <c r="J34" s="3">
         <v>46162</v>
       </c>
-      <c r="I34" s="3">
+      <c r="K34" s="3">
         <v>46162</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>93</v>
       </c>
@@ -2192,20 +2156,20 @@
       <c r="F35" t="s">
         <v>17</v>
       </c>
-      <c r="G35" t="s">
+      <c r="I35" t="s">
         <v>252</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>46163</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>46163</v>
       </c>
-      <c r="L35" t="s">
+      <c r="N35" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>95</v>
       </c>
@@ -2221,17 +2185,17 @@
       <c r="F36" t="s">
         <v>17</v>
       </c>
-      <c r="G36" t="s">
+      <c r="I36" t="s">
         <v>252</v>
       </c>
-      <c r="H36" s="3">
+      <c r="J36" s="3">
         <v>46163</v>
       </c>
-      <c r="I36" s="3">
+      <c r="K36" s="3">
         <v>46163</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>99</v>
       </c>
@@ -2247,20 +2211,20 @@
       <c r="F37" t="s">
         <v>17</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>252</v>
       </c>
-      <c r="H37" s="3">
+      <c r="J37" s="3">
         <v>46169</v>
       </c>
-      <c r="I37" s="3">
+      <c r="K37" s="3">
         <v>46169</v>
       </c>
-      <c r="L37" t="s">
+      <c r="N37" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>105</v>
       </c>
@@ -2276,20 +2240,20 @@
       <c r="F38" t="s">
         <v>17</v>
       </c>
-      <c r="G38" t="s">
+      <c r="I38" t="s">
         <v>252</v>
       </c>
-      <c r="H38" s="3">
+      <c r="J38" s="3">
         <v>46174</v>
       </c>
-      <c r="I38" s="3">
+      <c r="K38" s="3">
         <v>46174</v>
       </c>
-      <c r="L38" t="s">
+      <c r="N38" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -2305,14 +2269,8 @@
       <c r="F39" t="s">
         <v>17</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
         <v>252</v>
-      </c>
-      <c r="H39" s="3">
-        <v>46174</v>
-      </c>
-      <c r="I39" s="3">
-        <v>46174</v>
       </c>
       <c r="J39" s="3">
         <v>46174</v>
@@ -2320,11 +2278,17 @@
       <c r="K39" s="3">
         <v>46174</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L39" s="3">
+        <v>46174</v>
+      </c>
+      <c r="M39" s="3">
+        <v>46174</v>
+      </c>
+      <c r="N39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>108</v>
       </c>
@@ -2340,14 +2304,8 @@
       <c r="F40" t="s">
         <v>17</v>
       </c>
-      <c r="G40" t="s">
+      <c r="I40" t="s">
         <v>252</v>
-      </c>
-      <c r="H40" s="3">
-        <v>46174</v>
-      </c>
-      <c r="I40" s="3">
-        <v>46174</v>
       </c>
       <c r="J40" s="3">
         <v>46174</v>
@@ -2355,8 +2313,14 @@
       <c r="K40" s="3">
         <v>46174</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L40" s="3">
+        <v>46174</v>
+      </c>
+      <c r="M40" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>110</v>
       </c>
@@ -2372,14 +2336,8 @@
       <c r="F41" t="s">
         <v>17</v>
       </c>
-      <c r="G41" t="s">
+      <c r="I41" t="s">
         <v>252</v>
-      </c>
-      <c r="H41" s="3">
-        <v>46174</v>
-      </c>
-      <c r="I41" s="3">
-        <v>46174</v>
       </c>
       <c r="J41" s="3">
         <v>46174</v>
@@ -2387,8 +2345,14 @@
       <c r="K41" s="3">
         <v>46174</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3">
+        <v>46174</v>
+      </c>
+      <c r="M41" s="3">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>115</v>
       </c>
@@ -2404,63 +2368,63 @@
       <c r="F42" t="s">
         <v>17</v>
       </c>
-      <c r="G42" t="s">
+      <c r="I42" t="s">
         <v>252</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>46175</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>46176</v>
       </c>
     </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>45</v>
+      </c>
+      <c r="I43" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="E46" t="s">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:N42">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:P42">
     <sortCondition descending="1" ref="D1:D42"/>
   </sortState>
-  <conditionalFormatting sqref="H3:J42">
-    <cfRule type="containsBlanks" dxfId="2" priority="8">
-      <formula>LEN(TRIM(H3))=0</formula>
+  <conditionalFormatting sqref="J3:L42">
+    <cfRule type="containsBlanks" dxfId="3" priority="8">
+      <formula>LEN(TRIM(J3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:K2">
-    <cfRule type="containsBlanks" dxfId="9" priority="15">
-      <formula>LEN(TRIM(H2))=0</formula>
+  <conditionalFormatting sqref="J2:M2">
+    <cfRule type="containsBlanks" dxfId="2" priority="15">
+      <formula>LEN(TRIM(J2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1">
-    <cfRule type="containsBlanks" dxfId="8" priority="18">
-      <formula>LEN(TRIM(K1))=0</formula>
+  <conditionalFormatting sqref="M1">
+    <cfRule type="containsBlanks" dxfId="1" priority="18">
+      <formula>LEN(TRIM(M1))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K14 K16:K35 K42:K1048576 K37:K38">
-    <cfRule type="containsBlanks" dxfId="7" priority="7">
-      <formula>LEN(TRIM(K4))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K15">
-    <cfRule type="containsBlanks" dxfId="6" priority="6">
-      <formula>LEN(TRIM(K15))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K36">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
-      <formula>LEN(TRIM(K36))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3">
-    <cfRule type="containsBlanks" dxfId="3" priority="3">
-      <formula>LEN(TRIM(K3))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K39">
-    <cfRule type="containsBlanks" dxfId="1" priority="2">
-      <formula>LEN(TRIM(K39))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K40:K41">
+  <conditionalFormatting sqref="M3:M1048576">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(K40))=0</formula>
+      <formula>LEN(TRIM(M3))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
